--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1220-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1220-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5644A419-30F3-4F66-98B2-0E7A31505050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{76A9576F-F5D8-4D2B-956A-4AA9A2B35951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{45D7AFBC-EF89-4922-8018-E6A63C2A4C34}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{6B8A028B-4472-4C71-BD1F-CFD82CFFE654}"/>
   </bookViews>
   <sheets>
     <sheet name="1220-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1517,29 +1517,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D93D682B-9C86-4A8D-A2DF-729BD4182224}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0557A909-E3E7-4F83-B285-292FB6CA11A2}">
   <dimension ref="A1:X44"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1573,7 +1572,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1609,7 +1608,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1661,7 +1660,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1729,7 +1728,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2024</v>
       </c>
@@ -1801,7 +1800,7 @@
         <v>5.74</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>2023</v>
       </c>
@@ -1873,7 +1872,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="36">
         <v>2022</v>
       </c>
@@ -1945,7 +1944,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>2021</v>
       </c>
@@ -2017,7 +2016,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="36">
         <v>2020</v>
       </c>
@@ -2089,7 +2088,7 @@
         <v>8.77</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="38">
         <v>2019</v>
       </c>
@@ -2161,7 +2160,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="36">
         <v>2018</v>
       </c>
@@ -2233,7 +2232,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="38">
         <v>2017</v>
       </c>
@@ -2305,7 +2304,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="36">
         <v>2016</v>
       </c>
@@ -2377,7 +2376,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="38">
         <v>2015</v>
       </c>
@@ -2449,7 +2448,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="36">
         <v>2014</v>
       </c>
@@ -2521,7 +2520,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="38">
         <v>2013</v>
       </c>
@@ -2593,7 +2592,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="36">
         <v>2012</v>
       </c>
@@ -2665,7 +2664,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="38">
         <v>2011</v>
       </c>
@@ -2737,7 +2736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="36">
         <v>2010</v>
       </c>
@@ -2809,7 +2808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="38">
         <v>2009</v>
       </c>
@@ -2881,7 +2880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="36">
         <v>2008</v>
       </c>
@@ -2953,7 +2952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="38">
         <v>2007</v>
       </c>
@@ -3025,7 +3024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="36">
         <v>2006</v>
       </c>
@@ -3097,7 +3096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="38">
         <v>2005</v>
       </c>
@@ -3169,7 +3168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="36">
         <v>2004</v>
       </c>
@@ -3241,7 +3240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="38">
         <v>2003</v>
       </c>
@@ -3313,7 +3312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="36">
         <v>2002</v>
       </c>
@@ -3385,7 +3384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="38">
         <v>2001</v>
       </c>
@@ -3457,7 +3456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="36">
         <v>2000</v>
       </c>
@@ -3529,7 +3528,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="38">
         <v>1999</v>
       </c>
@@ -3601,7 +3600,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="36">
         <v>1998</v>
       </c>
@@ -3673,7 +3672,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="38">
         <v>1997</v>
       </c>
@@ -3745,7 +3744,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="36">
         <v>1996</v>
       </c>
@@ -3817,7 +3816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="38">
         <v>1995</v>
       </c>
@@ -3889,7 +3888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="36">
         <v>1994</v>
       </c>
@@ -3961,7 +3960,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="38">
         <v>1993</v>
       </c>
@@ -4033,7 +4032,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="36">
         <v>1992</v>
       </c>
@@ -4105,7 +4104,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="38">
         <v>1991</v>
       </c>
@@ -4177,7 +4176,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="36">
         <v>1990</v>
       </c>
@@ -4249,7 +4248,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="40">
         <v>1989</v>
       </c>
@@ -4321,7 +4320,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="42"/>
       <c r="B41" s="43"/>
       <c r="C41" s="19" t="s">
@@ -4349,7 +4348,7 @@
       <c r="W41" s="49"/>
       <c r="X41" s="45"/>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="36">
         <v>1988</v>
       </c>
@@ -4421,7 +4420,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="38">
         <v>1987</v>
       </c>
@@ -4493,7 +4492,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="36" t="s">
         <v>52</v>
       </c>
